--- a/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
+++ b/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
+++ b/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
+++ b/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
+++ b/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
+++ b/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
+++ b/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
+++ b/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
+++ b/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
+++ b/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
+++ b/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
+++ b/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
+++ b/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
+++ b/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
+++ b/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
+++ b/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
+++ b/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
+++ b/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
+++ b/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
+++ b/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
+++ b/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
+++ b/docs/ValueSet-VSVFVitalsDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
